--- a/output/pdf_financials_xlsx/SA.H.xlsx
+++ b/output/pdf_financials_xlsx/SA.H.xlsx
@@ -5659,25 +5659,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.926928</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>10.461028</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>11.498915</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>11.841937</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>11.922405</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>11.949662</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>12.177346</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -25376,7 +25376,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -26230,7 +26234,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -27558,7 +27566,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -28784,7 +28796,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E223" s="5" t="n">
         <v>5.926928</v>
       </c>

--- a/output/pdf_financials_xlsx/SA.H.xlsx
+++ b/output/pdf_financials_xlsx/SA.H.xlsx
@@ -1020,22 +1020,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.090294</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.278209</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.175684</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.060313</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.006678</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002726</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.583353</v>
+        <v>-6.673647</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.312411</v>
+        <v>-4.59062</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-41.94517</v>
+        <v>-42.120854</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8.680792</v>
+        <v>-8.741104999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.967266</v>
+        <v>-3.973944</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.976554</v>
+        <v>-0.97928</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.517035</v>
@@ -2097,22 +2097,22 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.577383</v>
+        <v>-6.667677</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.283405</v>
+        <v>-4.561614</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-41.91532</v>
+        <v>-42.091004</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.655726</v>
+        <v>-8.716039</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.95914</v>
+        <v>-3.965818</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.976356</v>
+        <v>-0.979082</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.493866</v>
@@ -2387,52 +2387,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.604476</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>38.632091</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>22.441567</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>12.866306</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.643966</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.053614</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.273186</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>11.763403</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.573385</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.435968</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.349773</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.63007</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.045281</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.1838</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.014412</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.006515</v>
       </c>
     </row>
     <row r="35">
@@ -2497,52 +2497,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.604476</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>38.632091</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>22.441567</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>12.866306</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.643966</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.053614</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.273186</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.55</v>
+        <v>12.313403</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.573385</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.435968</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.349773</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.63007</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.045281</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.1838</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.014412</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.006515</v>
       </c>
     </row>
     <row r="37">
@@ -3157,52 +3157,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.447809</v>
+        <v>0.843333</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>38.726907</v>
+        <v>0.094816</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>22.558847</v>
+        <v>0.11728</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>16.607259</v>
+        <v>3.740953</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.863073</v>
+        <v>1.219107</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.078252</v>
+        <v>0.024638</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.286223</v>
+        <v>0.013037</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>11.938799</v>
+        <v>0.175396</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.223584</v>
+        <v>2.650199</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.996909</v>
+        <v>1.560941</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.501593</v>
+        <v>1.15182</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.501836</v>
+        <v>0.871766</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.140049</v>
+        <v>0.09476800000000001</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.454363</v>
+        <v>0.270563</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.274018</v>
+        <v>0.259606</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.075221</v>
+        <v>0.068706</v>
       </c>
     </row>
     <row r="49">
@@ -7453,10 +7453,10 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.104243</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.025633</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -7510,10 +7510,10 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.104243</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.025633</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -32588,7 +32588,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -60962,7 +60966,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -62970,7 +62974,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -66472,7 +66476,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">

--- a/output/pdf_financials_xlsx/SA.H.xlsx
+++ b/output/pdf_financials_xlsx/SA.H.xlsx
@@ -1320,10 +1320,10 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.274334</v>
+        <v>-0.274334</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.274205</v>
+        <v>0.274205</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -6871,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.04974</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -6886,13 +6886,13 @@
         <v>0</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-0.266062</v>
       </c>
       <c r="N114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="P114" s="3" t="n">
         <v>0</v>
@@ -6928,13 +6928,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>1.172588</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>13.813237</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>3.6474</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.8667280000000001</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
@@ -6955,7 +6955,7 @@
         <v>0.03594</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.06814099999999999</v>
       </c>
     </row>
     <row r="116">
@@ -29760,7 +29760,11 @@
           <t>Proceeds from sale of investments (Note 3a and 3b)</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -30618,7 +30622,11 @@
           <t>Acquisition of investment (Note 3)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -31568,7 +31576,11 @@
           <t>Proceeds from sale of investments (Note 3)</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -32210,7 +32222,11 @@
           <t>Acquisition of investment</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -34452,7 +34468,11 @@
           <t>Cash received from private placement</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -38068,7 +38088,11 @@
           <t>Proceeds from sale of investments, net (Note 4)</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -39968,7 +39992,11 @@
           <t>Proceeds from sale of investments, net (Note 4)</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -42528,7 +42556,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -42624,7 +42656,11 @@
           <t>Share issue costs for private placement</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -44232,7 +44268,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -59532,7 +59572,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
@@ -61828,7 +61872,11 @@
           <t>Income tax recovery $</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E572" t="inlineStr">
         <is>
           <t>-</t>
